--- a/new_data.xlsx
+++ b/new_data.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gpd_records" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="users" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="campus_records" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="church_records" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="users" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O227"/>
+  <dimension ref="A1:J224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,37 +473,12 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>image_path</t>
+          <t>images_json</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>image1_path</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>image2_path</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>image3_path</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>image4_path</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>images_json</t>
         </is>
       </c>
     </row>
@@ -539,37 +515,12 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>/images/pASTOR_derrick_izekor_20251213.jpg</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>/images/pastor_derrick_izekor_20260103_164133.png</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>/images/pastor_derrick_izekor_20260103_164133.png</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>/images/pastor_derrick_izekor_20260103_164133.png</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>/images/pastor_derrick_izekor_20260103_164133.png</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>["/images/pastor_derrick_izekor_20260105_121713_215985.jpeg", "/images/pastor_derrick_izekor_20260105_121713_260246.jpg", "/images/pastor_derrick_izekor_20260105_121713_260246.webp", "/images/pastor_derrick_izekor_20260105_121713_268747.jpeg"]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -600,19 +551,14 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -643,19 +589,14 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -686,19 +627,14 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -729,19 +665,14 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -772,19 +703,14 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -815,19 +741,14 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -858,19 +779,14 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -901,19 +817,14 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -944,19 +855,14 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -987,19 +893,14 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1030,19 +931,14 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1073,19 +969,14 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1116,19 +1007,14 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1159,19 +1045,14 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1202,19 +1083,14 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1245,19 +1121,14 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1288,19 +1159,14 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1331,19 +1197,14 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1374,19 +1235,14 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1417,19 +1273,14 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1460,19 +1311,14 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1503,19 +1349,14 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1546,19 +1387,14 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1589,19 +1425,14 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1632,19 +1463,14 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1675,19 +1501,14 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1718,19 +1539,14 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1761,19 +1577,14 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1804,19 +1615,14 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1847,19 +1653,14 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1890,19 +1691,14 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1933,19 +1729,14 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -1976,19 +1767,14 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2019,19 +1805,14 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2062,19 +1843,14 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2105,19 +1881,14 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2148,19 +1919,14 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2191,19 +1957,14 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2234,19 +1995,14 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2277,19 +2033,14 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2316,19 +2067,14 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2355,19 +2101,14 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2398,19 +2139,14 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2441,19 +2177,14 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2484,19 +2215,14 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2527,19 +2253,14 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2570,19 +2291,14 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2613,19 +2329,14 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2656,19 +2367,14 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2699,19 +2405,14 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2742,19 +2443,14 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2785,19 +2481,14 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2828,19 +2519,14 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2871,19 +2557,14 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2914,19 +2595,14 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -2953,19 +2629,14 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:15</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3000,19 +2671,14 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3045,25 +2711,16 @@
           <t>BLW SA Zone A</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Wits Group</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3088,25 +2745,16 @@
           <t>BLW SA Zone A</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Limpopo Group</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3131,25 +2779,16 @@
           <t>BLW SA Zone A</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Vaal–NorthWest Group</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3174,25 +2813,16 @@
           <t>BLW SA Zone A</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Mpumalanga Group</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3217,25 +2847,16 @@
           <t>BLW SA Zone A</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Eswatini Group</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3262,19 +2883,14 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3299,25 +2915,16 @@
           <t>BLW SA Zone B</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Durban Group</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3342,25 +2949,16 @@
           <t>BLW SA Zone B</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>South Coast Group</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3385,25 +2983,16 @@
           <t>BLW SA Zone B</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>East London &amp; Mthatha Group</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3428,25 +3017,16 @@
           <t>BLW SA Zone B</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Grahamstown &amp; Alice Group</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3471,25 +3051,16 @@
           <t>BLW SA Zone B</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Port Elizabeth Group</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3516,19 +3087,14 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3553,25 +3119,16 @@
           <t>BLW SA Zone C</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Western Cape Group</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3596,25 +3153,16 @@
           <t>BLW SA Zone C</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Free State Group</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3641,19 +3189,14 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3678,25 +3221,16 @@
           <t>BLW SA Zone D</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Harare Group</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3721,25 +3255,16 @@
           <t>BLW SA Zone D</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Harare South</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3764,25 +3289,16 @@
           <t>BLW SA Zone D</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Manicaland</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3807,25 +3323,16 @@
           <t>BLW SA Zone D</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Midlands</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3850,25 +3357,16 @@
           <t>BLW SA Zone D</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>City of Kings</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3893,25 +3391,16 @@
           <t>BLW SA Zone D</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Mashonaland West</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3936,25 +3425,16 @@
           <t>BLW SA Zone D</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Mashonaland East</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -3979,25 +3459,16 @@
           <t>BLW SA Zone D</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Masvingo</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4024,19 +3495,14 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4061,25 +3527,16 @@
           <t>BLW SA Zone E</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>University of Botswana</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4104,25 +3561,16 @@
           <t>BLW SA Zone E</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Botswana Group 1</t>
-        </is>
-      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4149,19 +3597,14 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4186,25 +3629,16 @@
           <t>BLW SA Zone F</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Khomas Group</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4229,25 +3663,16 @@
           <t>BLW SA Zone F</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Oshana Group</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4274,19 +3699,14 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4311,25 +3731,16 @@
           <t>BLW SA Zone H</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Lusaka Group</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4354,25 +3765,16 @@
           <t>BLW SA Zone H</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Copperbelt Group</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4395,19 +3797,14 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4432,25 +3829,16 @@
           <t>BLW SA Zone I</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Malawi South</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4475,25 +3863,16 @@
           <t>BLW SA Zone I</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Malawi North</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4518,25 +3897,16 @@
           <t>BLW SA Zone I</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Blantyre</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4559,19 +3929,14 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4600,25 +3965,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>UJ Group</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4643,25 +3999,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Lighthouse Group</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4686,25 +4033,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>JHB North Group</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4729,25 +4067,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Pretoria East Group</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4774,19 +4103,14 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4811,25 +4135,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>APK Chapter</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4854,25 +4169,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>APB Chapter</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4897,25 +4203,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>DFC Chapter</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4940,25 +4237,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Lighthouse</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -4983,25 +4271,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>LH GA Chapter</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5026,25 +4305,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Eduvos Chapter</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5069,25 +4339,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>IIE MSA Chapter</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5112,25 +4373,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>UP TUT Main Chapter</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5155,25 +4407,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>UP Groenkloof Chapter</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5198,25 +4441,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>CJC Chapter</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5241,25 +4475,16 @@
           <t>BLW SA Zone G</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>SWC Chapter</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5294,19 +4519,14 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5345,19 +4565,14 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5392,19 +4607,14 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5439,19 +4649,14 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5486,19 +4691,14 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5533,19 +4733,14 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5580,19 +4775,14 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5627,19 +4817,14 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5674,19 +4859,14 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5721,19 +4901,14 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5768,19 +4943,14 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5815,19 +4985,14 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5862,19 +5027,14 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5909,19 +5069,14 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -5956,19 +5111,14 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6003,19 +5153,14 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6050,19 +5195,14 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6097,19 +5237,14 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6144,19 +5279,14 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6191,19 +5321,14 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6238,19 +5363,14 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6285,19 +5405,14 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6332,19 +5447,14 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6379,19 +5489,14 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6426,19 +5531,14 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6473,19 +5573,14 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6520,19 +5615,14 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6567,19 +5657,14 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6614,19 +5699,14 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6661,19 +5741,14 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6708,19 +5783,14 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6755,19 +5825,14 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6802,19 +5867,14 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6849,19 +5909,14 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6896,19 +5951,14 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6943,19 +5993,14 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -6990,19 +6035,14 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7037,19 +6077,14 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7084,19 +6119,14 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7131,19 +6161,14 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7178,19 +6203,14 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7225,19 +6245,14 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7272,19 +6287,14 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7319,19 +6329,14 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7362,19 +6367,14 @@
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7405,19 +6405,14 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7448,19 +6443,14 @@
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7491,19 +6481,14 @@
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7534,19 +6519,14 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7577,19 +6557,14 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7620,19 +6595,14 @@
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7663,19 +6633,14 @@
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7706,19 +6671,14 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7749,19 +6709,14 @@
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7792,19 +6747,14 @@
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7835,19 +6785,14 @@
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7878,19 +6823,14 @@
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7921,19 +6861,14 @@
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -7964,19 +6899,14 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8007,19 +6937,14 @@
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8050,19 +6975,14 @@
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8093,19 +7013,14 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8136,19 +7051,14 @@
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8179,19 +7089,14 @@
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8222,19 +7127,14 @@
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8265,19 +7165,14 @@
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8308,19 +7203,14 @@
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8351,19 +7241,14 @@
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8394,19 +7279,14 @@
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8437,19 +7317,14 @@
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8480,19 +7355,14 @@
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8523,19 +7393,14 @@
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8566,19 +7431,14 @@
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8609,19 +7469,14 @@
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8652,19 +7507,14 @@
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8695,19 +7545,14 @@
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8738,19 +7583,14 @@
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8781,19 +7621,14 @@
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8824,19 +7659,14 @@
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8867,19 +7697,14 @@
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8910,19 +7735,14 @@
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8953,19 +7773,14 @@
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -8996,19 +7811,14 @@
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9039,19 +7849,14 @@
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9086,19 +7891,14 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9133,19 +7933,14 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9180,19 +7975,14 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9227,19 +8017,14 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9274,19 +8059,14 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9321,19 +8101,14 @@
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9364,19 +8139,14 @@
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9411,19 +8181,14 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9458,19 +8223,14 @@
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9505,19 +8265,14 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9552,19 +8307,14 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9599,19 +8349,14 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9646,19 +8391,14 @@
       </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9693,19 +8433,14 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9740,19 +8475,14 @@
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9787,19 +8517,14 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9834,19 +8559,14 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9881,19 +8601,14 @@
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9928,19 +8643,14 @@
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -9975,19 +8685,14 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -10022,19 +8727,14 @@
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -10069,19 +8769,14 @@
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -10116,19 +8811,14 @@
       </c>
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -10163,19 +8853,14 @@
       </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -10210,19 +8895,14 @@
       </c>
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -10257,19 +8937,14 @@
       </c>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -10304,19 +8979,14 @@
       </c>
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -10351,152 +9021,14 @@
       </c>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>2025-12-13 15:16:16</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>224</v>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>nigeria region</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>zonal pastor</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>ABUBAKAR ALLI</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>abbubakar</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>blw zone j</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>group e</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>medilag</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>2025-12-13 15:21:17</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>225</v>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>East and Central Africa Region</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Ag. Zonal Secretary</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Pastor Beatrice Ogolla</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>2025-12-14 13:11:44</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>226</v>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Europe Region</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Ag. Zonal Secretary</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>Pastor Kristina Fernandes</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>2025-12-14 13:11:44</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>2026-01-07 14:06:08</t>
         </is>
       </c>
     </row>
@@ -10511,6 +9043,414 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dsp</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>virtual_zone</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sub_group</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>church</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>reg_sub</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>designation</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kc_id</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>images_json</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CE Zone 2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional Pastor </t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Pastor Emmanuel Dingba</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>emmanueldingba</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-01-07 14:06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CE  Zone 2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CE Randburg Church</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Zonal Pastor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Pastor Freedom Eriya</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-01-07 14:06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CE Zone 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CE Pretoria</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Zonal Pastor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Pastor Lawrence Ajiboye</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-01-07 14:06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CE Zone 4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Zonal Pastor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pastor Dipo Fisho</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-01-07 14:06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CE Zone 3 DSP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Zonal Pastor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Pastor Kemi Adesina</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-01-07 14:06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UK  Region 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CE Zone 4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CE Nottingham group</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Zonal Pastor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Pastor Elizabeth Akinwolemiwa</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-01-07 14:06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CE Zone 3 DSP</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Masha</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CE Adekunle kuye</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>RZM</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Sister Grace Daniel</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>graced</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-01-07 14:06:15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -10542,7 +9482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pbkdf2:sha256:600000$f9LUWvO7kRhRHUgM$7ef8250700ee81d32171d357242832067bc303d0c76ef0542833d3e59e745ec2</t>
+          <t>pbkdf2:sha256:600000$kVC6q5H4DAklUDkB$6c0e11e130ded4a0de2b5a3fe1aa58b285dcafbbab16058a608eedbb7b6866a6</t>
         </is>
       </c>
     </row>
